--- a/backend/data/financials_by_company/001236.SZ.xlsx
+++ b/backend/data/financials_by_company/001236.SZ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,614 +677,669 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1813863.724242</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.221023</v>
-      </c>
-      <c r="D2" t="n">
-        <v>70914252.81999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8206658.87</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8206658.87</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29826197.5</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>34280158.06</v>
+        <v>20814612.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2696374815.43</v>
-      </c>
-      <c r="J2" t="n">
-        <v>79120911.69</v>
-      </c>
-      <c r="K2" t="n">
-        <v>44840753.63</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-6551801.35</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6551801.35</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>23433402.354242</v>
-      </c>
-      <c r="P2" t="n">
-        <v>29826197.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2801382577.96</v>
-      </c>
+        <v>167041955.13</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>84118225.19</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>7237618.63</v>
-      </c>
-      <c r="S2" t="n">
-        <v>34642820.24</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1007641807</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1007641807</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.0296</v>
-      </c>
-      <c r="X2" t="n">
-        <v>29826197.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>29826197.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>29826197.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>29826197.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>29826197.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8462754.779999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>38288952.28</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4041932.15</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-11313193.67</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>429085.09</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>10884108.58</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-6551801.35</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>6551801.35</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>32549579.56</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>105007762.53</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>72531209.37</v>
-      </c>
+        <v>10761540.27</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>84118225.19</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>34280158.06</v>
+        <v>20814612.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>34280158.06</v>
+        <v>20814612.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>1761496.15</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>12057289.56</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12057289.56</v>
-      </c>
+        <v>851347.96</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>7237618.63</v>
+        <v>10761540.27</v>
       </c>
       <c r="AV2" t="n">
-        <v>137557342.09</v>
+        <v>1458594866.81</v>
       </c>
       <c r="AW2" t="n">
-        <v>2696374815.43</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2833932157.52</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2833932157.52</v>
-      </c>
+        <v>167041955.13</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1283795.584733</v>
+        <v>645310.110436</v>
       </c>
       <c r="C3" t="n">
-        <v>0.255972</v>
+        <v>0.221612</v>
       </c>
       <c r="D3" t="n">
-        <v>46891946.52</v>
+        <v>40010667.03</v>
       </c>
       <c r="E3" t="n">
-        <v>5015368.04</v>
+        <v>2911896.55</v>
       </c>
       <c r="F3" t="n">
-        <v>5015368.04</v>
+        <v>2911896.55</v>
       </c>
       <c r="G3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="H3" t="n">
-        <v>33758765.43</v>
+        <v>18962918.31</v>
       </c>
       <c r="I3" t="n">
-        <v>1816158660.34</v>
+        <v>1418972636.63</v>
       </c>
       <c r="J3" t="n">
-        <v>51907314.56</v>
+        <v>42922563.58</v>
       </c>
       <c r="K3" t="n">
-        <v>18148549.13</v>
+        <v>23959645.27</v>
       </c>
       <c r="L3" t="n">
-        <v>-7676496.92</v>
+        <v>-8052535.9</v>
       </c>
       <c r="M3" t="n">
-        <v>7676496.92</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>8052535.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>92221690.44</v>
+      </c>
       <c r="O3" t="n">
-        <v>4059923.854733</v>
+        <v>10115322.660436</v>
       </c>
       <c r="P3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1893819829.35</v>
+        <v>1528389327.59</v>
       </c>
       <c r="R3" t="n">
-        <v>5721320.87</v>
+        <v>7215024.45</v>
       </c>
       <c r="S3" t="n">
-        <v>6549979.03</v>
+        <v>15971750.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1011882638</v>
+        <v>938023417</v>
       </c>
       <c r="U3" t="n">
-        <v>1011882638</v>
+        <v>938023417</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0077</v>
+        <v>0.0132</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0077</v>
+        <v>0.0132</v>
       </c>
       <c r="X3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>2680555.9</v>
+        <v>3525200.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>10472052.21</v>
+        <v>15907109.37</v>
       </c>
       <c r="AF3" t="n">
-        <v>-8520409.59</v>
+        <v>14513450.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>-845241.16</v>
+        <v>2911896.55</v>
       </c>
       <c r="AH3" t="n">
-        <v>289900.94</v>
+        <v>102386.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>555340.22</v>
+        <v>-3014282.88</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-7676496.92</v>
+        <v>-8052535.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>7676496.92</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>8052535.9</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>92221690.44</v>
+      </c>
       <c r="AM3" t="n">
-        <v>21198304.26</v>
+        <v>-4551992.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>77661169.01000001</v>
+        <v>109416690.96</v>
       </c>
       <c r="AO3" t="n">
-        <v>66856022.32</v>
+        <v>93190718.01000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>33758765.43</v>
+        <v>18962918.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>33758765.43</v>
+        <v>18962918.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>2045984.26</v>
+        <v>1648318.92</v>
       </c>
       <c r="AS3" t="n">
-        <v>5143377.14</v>
+        <v>7141597.57</v>
       </c>
       <c r="AT3" t="n">
-        <v>5143377.14</v>
+        <v>7141597.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>5721320.87</v>
+        <v>7215024.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>98859473.27</v>
+        <v>104864698.04</v>
       </c>
       <c r="AW3" t="n">
-        <v>1816158660.34</v>
+        <v>1418972636.63</v>
       </c>
       <c r="AX3" t="n">
-        <v>1915018133.61</v>
+        <v>1523837334.67</v>
       </c>
       <c r="AY3" t="n">
-        <v>1915018133.61</v>
+        <v>1523837334.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>645310.110436</v>
+        <v>1283795.584733</v>
       </c>
       <c r="C4" t="n">
-        <v>0.221612</v>
+        <v>0.255972</v>
       </c>
       <c r="D4" t="n">
-        <v>40010667.03</v>
+        <v>46891946.52</v>
       </c>
       <c r="E4" t="n">
-        <v>2911896.55</v>
+        <v>5015368.04</v>
       </c>
       <c r="F4" t="n">
-        <v>2911896.55</v>
+        <v>5015368.04</v>
       </c>
       <c r="G4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="H4" t="n">
-        <v>18962918.31</v>
+        <v>33758765.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1418972636.63</v>
+        <v>1816158660.34</v>
       </c>
       <c r="J4" t="n">
-        <v>42922563.58</v>
+        <v>51907314.56</v>
       </c>
       <c r="K4" t="n">
-        <v>23959645.27</v>
+        <v>18148549.13</v>
       </c>
       <c r="L4" t="n">
-        <v>-8052535.9</v>
+        <v>-7676496.92</v>
       </c>
       <c r="M4" t="n">
-        <v>8052535.9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>92221690.44</v>
-      </c>
+        <v>7676496.92</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>10115322.660436</v>
+        <v>4059923.854733</v>
       </c>
       <c r="P4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>1528389327.59</v>
+        <v>1893819829.35</v>
       </c>
       <c r="R4" t="n">
-        <v>7215024.45</v>
+        <v>5721320.87</v>
       </c>
       <c r="S4" t="n">
-        <v>15971750.15</v>
+        <v>6549979.03</v>
       </c>
       <c r="T4" t="n">
-        <v>938023417</v>
+        <v>1011882638</v>
       </c>
       <c r="U4" t="n">
-        <v>938023417</v>
+        <v>1011882638</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0132</v>
+        <v>0.0077</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0132</v>
+        <v>0.0077</v>
       </c>
       <c r="X4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="Y4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="AB4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="AD4" t="n">
-        <v>3525200.27</v>
+        <v>2680555.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>15907109.37</v>
+        <v>10472052.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>14513450.57</v>
+        <v>-8520409.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>2911896.55</v>
+        <v>-845241.16</v>
       </c>
       <c r="AH4" t="n">
-        <v>102386.33</v>
+        <v>289900.94</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3014282.88</v>
+        <v>555340.22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-8052535.9</v>
+        <v>-7676496.92</v>
       </c>
       <c r="AK4" t="n">
-        <v>8052535.9</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>92221690.44</v>
-      </c>
+        <v>7676496.92</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-4551992.92</v>
+        <v>21198304.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>109416690.96</v>
+        <v>77661169.01000001</v>
       </c>
       <c r="AO4" t="n">
-        <v>93190718.01000001</v>
+        <v>66856022.32</v>
       </c>
       <c r="AP4" t="n">
-        <v>18962918.31</v>
+        <v>33758765.43</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18962918.31</v>
+        <v>33758765.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>1648318.92</v>
+        <v>2045984.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>7141597.57</v>
+        <v>5143377.14</v>
       </c>
       <c r="AT4" t="n">
-        <v>7141597.57</v>
+        <v>5143377.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>7215024.45</v>
+        <v>5721320.87</v>
       </c>
       <c r="AV4" t="n">
-        <v>104864698.04</v>
+        <v>98859473.27</v>
       </c>
       <c r="AW4" t="n">
-        <v>1418972636.63</v>
+        <v>1816158660.34</v>
       </c>
       <c r="AX4" t="n">
-        <v>1523837334.67</v>
+        <v>1915018133.61</v>
       </c>
       <c r="AY4" t="n">
-        <v>1523837334.67</v>
+        <v>1915018133.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-176100.22653</v>
+        <v>100013.066286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.265545</v>
+        <v>0.221023</v>
       </c>
       <c r="D5" t="n">
-        <v>139053195.21</v>
+        <v>38372146.79</v>
       </c>
       <c r="E5" t="n">
-        <v>-663166.14</v>
+        <v>452499.88</v>
       </c>
       <c r="F5" t="n">
-        <v>-663166.14</v>
+        <v>452499.88</v>
       </c>
       <c r="G5" t="n">
-        <v>80211471.47</v>
+        <v>29826197.5</v>
       </c>
       <c r="H5" t="n">
-        <v>20814612.1</v>
+        <v>34280158.06</v>
       </c>
       <c r="I5" t="n">
-        <v>167041955.13</v>
+        <v>2696374815.43</v>
       </c>
       <c r="J5" t="n">
-        <v>138390029.07</v>
+        <v>38824646.67</v>
       </c>
       <c r="K5" t="n">
-        <v>117575416.97</v>
+        <v>38824646.67</v>
       </c>
       <c r="L5" t="n">
-        <v>-8363233.47</v>
+        <v>-535694.39</v>
       </c>
       <c r="M5" t="n">
-        <v>8363233.47</v>
-      </c>
-      <c r="N5" t="n">
-        <v>84118225.19</v>
-      </c>
+        <v>535694.39</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>80698537.38347</v>
+        <v>29473710.686286</v>
       </c>
       <c r="P5" t="n">
-        <v>80211471.47</v>
+        <v>29826197.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1501142940.04</v>
+        <v>299184111.06</v>
       </c>
       <c r="R5" t="n">
-        <v>10761540.27</v>
+        <v>7237618.63</v>
       </c>
       <c r="S5" t="n">
-        <v>109914011.28</v>
+        <v>34642820.24</v>
       </c>
       <c r="T5" t="n">
-        <v>907369587</v>
+        <v>1007641807</v>
       </c>
       <c r="U5" t="n">
-        <v>907369587</v>
+        <v>1007641807</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0296</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0296</v>
       </c>
       <c r="X5" t="n">
-        <v>80211471.47</v>
+        <v>29826197.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>80211471.47</v>
+        <v>29826197.5</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>80211471.47</v>
+        <v>29826197.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>80211471.47</v>
+        <v>29826197.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>80211471.47</v>
+        <v>29826197.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>29000712.03</v>
+        <v>8462754.779999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>109212183.5</v>
+        <v>38288952.28</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4345494.72</v>
+        <v>3646132.04</v>
       </c>
       <c r="AG5" t="n">
-        <v>-663166.14</v>
+        <v>452499.88</v>
       </c>
       <c r="AH5" t="n">
-        <v>398068.76</v>
+        <v>40341.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>265097.38</v>
+        <v>-492840.97</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-8363233.47</v>
+        <v>-535694.39</v>
       </c>
       <c r="AK5" t="n">
-        <v>8363233.47</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>84118225.19</v>
-      </c>
+        <v>535694.39</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>124493881.9</v>
+        <v>35034603.94</v>
       </c>
       <c r="AN5" t="n">
-        <v>1334100984.91</v>
+        <v>299184111.06</v>
       </c>
       <c r="AO5" t="n">
-        <v>1330790452.59</v>
+        <v>17701339.01</v>
       </c>
       <c r="AP5" t="n">
-        <v>20814612.1</v>
+        <v>34280158.06</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20814612.1</v>
+        <v>34280158.06</v>
       </c>
       <c r="AR5" t="n">
-        <v>851347.96</v>
+        <v>1761496.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>6816602.73</v>
+        <v>309985842.24</v>
       </c>
       <c r="AT5" t="n">
-        <v>6816602.73</v>
+        <v>309985842.24</v>
       </c>
       <c r="AU5" t="n">
-        <v>10761540.27</v>
+        <v>7237618.63</v>
       </c>
       <c r="AV5" t="n">
-        <v>1458594866.81</v>
+        <v>137557342.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>167041955.13</v>
+        <v>2696374815.43</v>
       </c>
       <c r="AX5" t="n">
-        <v>1625636821.94</v>
+        <v>334218715</v>
       </c>
       <c r="AY5" t="n">
-        <v>1625636821.94</v>
+        <v>334218715</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-21679.258372</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.080521</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4625537.54</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-269238.65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-269238.65</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3992694.29</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>4356298.89</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4356298.89</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-13956.58</v>
+      </c>
+      <c r="M6" t="n">
+        <v>13956.58</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>4240253.681628</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3992694.29</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>236198138.01</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>3727547.59</v>
+      </c>
+      <c r="T6" t="n">
+        <v>998173572</v>
+      </c>
+      <c r="U6" t="n">
+        <v>998173572</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3992694.29</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3992694.29</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3992694.29</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3992694.29</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3992694.29</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>349648.02</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>4342342.31</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>614794.72</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-269238.65</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>876465.42</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-607226.77</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-13956.58</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>13956.58</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>4116282.74</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>236198138.01</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>15218783.86</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>269212441.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>269212441.9</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>240314420.75</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>240314420.75</v>
       </c>
     </row>
   </sheetData>
@@ -1298,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL5"/>
+  <dimension ref="A1:BM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1617,194 +1672,96 @@
           <t>Cash Equivalents</t>
         </is>
       </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1007777778</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1007777778</v>
-      </c>
-      <c r="D2" t="n">
-        <v>286946002.54</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1875707709.59</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2148050245.07</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1635164357.45</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1875707709.59</v>
-      </c>
-      <c r="I2" t="n">
-        <v>15674410.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1876778653.33</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1876778653.33</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1876778653.33</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1876778653.33</v>
-      </c>
-      <c r="N2" t="n">
-        <v>86784552.34</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1007777778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1007777778</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>9822590967.549999</v>
-      </c>
-      <c r="R2" t="n">
-        <v>205673263.81</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>9859658.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3392469.65</v>
-      </c>
-      <c r="V2" t="n">
-        <v>15674410.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>15674410.8</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>176746725.35</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9616917703.74</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>271271591.74</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>271271591.74</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6830112.98</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>9330903236.93</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>9328989181.360001</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>1914055.57</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>11699369620.88</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>447287559.69</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>18349584.85</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>11556875.02</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1969920.97</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>117197967.93</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>3585849.06</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>8824536.85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>29736228.88</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>29736228.88</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8709774.279999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>48467078</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1070943.74</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1070943.74</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>320572538.07</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-159468366.64</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>480040904.71</v>
-      </c>
+        <v>1808800</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>56359246.37</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>326706062.94</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>96975595.40000001</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>11252082061.19</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6778156567.1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>26866747.17</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>409626350.92</v>
-      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>409626350.92</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3187995721.42</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>63966816.41</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>785469858.17</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>376949131.71</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>408520726.46</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>408520726.46</v>
-      </c>
+        <v>9531.74</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1007777778</v>
@@ -1813,37 +1770,37 @@
         <v>1007777778</v>
       </c>
       <c r="D3" t="n">
-        <v>191266024.67</v>
+        <v>146945153.38</v>
       </c>
       <c r="E3" t="n">
-        <v>1846949573.5</v>
+        <v>1836787947.18</v>
       </c>
       <c r="F3" t="n">
-        <v>2015106165.2</v>
+        <v>1961695747.09</v>
       </c>
       <c r="G3" t="n">
-        <v>1689378815.91</v>
+        <v>1690778367.41</v>
       </c>
       <c r="H3" t="n">
-        <v>1846949573.5</v>
+        <v>1836787947.18</v>
       </c>
       <c r="I3" t="n">
-        <v>23653164.97</v>
+        <v>22573315.47</v>
       </c>
       <c r="J3" t="n">
-        <v>1847493305.5</v>
+        <v>1837323909.18</v>
       </c>
       <c r="K3" t="n">
-        <v>1908636072.31</v>
+        <v>1926498514.41</v>
       </c>
       <c r="L3" t="n">
-        <v>1847493305.5</v>
+        <v>1837323909.18</v>
       </c>
       <c r="M3" t="n">
-        <v>1847493305.5</v>
+        <v>1837323909.18</v>
       </c>
       <c r="N3" t="n">
-        <v>65935375.99</v>
+        <v>60537412.94</v>
       </c>
       <c r="O3" t="n">
         <v>1007777778</v>
@@ -1852,141 +1809,146 @@
         <v>1007777778</v>
       </c>
       <c r="Q3" t="n">
-        <v>7465583838.39</v>
+        <v>8646604790.549999</v>
       </c>
       <c r="R3" t="n">
-        <v>268083184.23</v>
+        <v>295172468.58</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>14064892.26</v>
+        <v>22573170.18</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>84795931.78</v>
+        <v>111747920.7</v>
       </c>
       <c r="W3" t="n">
-        <v>23653164.97</v>
+        <v>22573315.47</v>
       </c>
       <c r="X3" t="n">
-        <v>61142766.81</v>
+        <v>89174605.23</v>
       </c>
       <c r="Y3" t="n">
-        <v>169222360.19</v>
+        <v>160851377.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>7197500654.16</v>
+        <v>8351432321.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>106470092.89</v>
+        <v>35197232.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>106470092.89</v>
+        <v>35197232.68</v>
       </c>
       <c r="AC3" t="n">
-        <v>2303860.56</v>
+        <v>2882801.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>7026746175.43</v>
+        <v>8226906886.69</v>
       </c>
       <c r="AE3" t="n">
-        <v>7024691578.18</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>8193524967.3</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>30233333.34</v>
+      </c>
       <c r="AG3" t="n">
-        <v>2054597.25</v>
+        <v>3148586.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>9313077143.889999</v>
+        <v>10483928699.73</v>
       </c>
       <c r="AI3" t="n">
-        <v>426197673.82</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>441718010.35</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>27308606.63</v>
+      </c>
       <c r="AK3" t="n">
-        <v>21001079.72</v>
+        <v>16637688.15</v>
       </c>
       <c r="AL3" t="n">
-        <v>5212428.02</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
-        <v>1853110</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1853110</v>
-      </c>
+        <v>19223235.33</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1846635</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>8252558.04</v>
+        <v>8252386.71</v>
       </c>
       <c r="AQ3" t="n">
-        <v>48573122</v>
+        <v>48420728</v>
       </c>
       <c r="AR3" t="n">
-        <v>543732</v>
+        <v>535962</v>
       </c>
       <c r="AS3" t="n">
-        <v>543732</v>
+        <v>535962</v>
       </c>
       <c r="AT3" t="n">
-        <v>340761644.04</v>
+        <v>346801375.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>-138998106.21</v>
+        <v>-107645788.97</v>
       </c>
       <c r="AV3" t="n">
-        <v>479759750.25</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>454447164.13</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
       <c r="AX3" t="n">
-        <v>57280797.38</v>
+        <v>49000772.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>320841455.43</v>
+        <v>320162830.99</v>
       </c>
       <c r="AZ3" t="n">
-        <v>101637497.44</v>
+        <v>85283560.44</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>8886879470.07</v>
+        <v>10042210689.38</v>
       </c>
       <c r="BC3" t="n">
-        <v>4426745702.71</v>
+        <v>6026696688.51</v>
       </c>
       <c r="BD3" t="n">
-        <v>50945132.39</v>
+        <v>27542988.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>64018473.68</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>64018473.68</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>3507044966.09</v>
+        <v>3128111550.07</v>
       </c>
       <c r="BH3" t="n">
-        <v>12463648.38</v>
+        <v>10186154.63</v>
       </c>
       <c r="BI3" t="n">
-        <v>825661546.8200001</v>
+        <v>849673307.22</v>
       </c>
       <c r="BJ3" t="n">
-        <v>436635183.99</v>
+        <v>558851538.15</v>
       </c>
       <c r="BK3" t="n">
-        <v>389026362.83</v>
+        <v>290821769.07</v>
       </c>
       <c r="BL3" t="n">
-        <v>389026362.83</v>
-      </c>
+        <v>290821769.07</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1007777778</v>
@@ -1995,37 +1957,37 @@
         <v>1007777778</v>
       </c>
       <c r="D4" t="n">
-        <v>146945153.38</v>
+        <v>191266024.67</v>
       </c>
       <c r="E4" t="n">
-        <v>1836787947.18</v>
+        <v>1846949573.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1961695747.09</v>
+        <v>2015106165.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1690778367.41</v>
+        <v>1689378815.91</v>
       </c>
       <c r="H4" t="n">
-        <v>1836787947.18</v>
+        <v>1846949573.5</v>
       </c>
       <c r="I4" t="n">
-        <v>22573315.47</v>
+        <v>23653164.97</v>
       </c>
       <c r="J4" t="n">
-        <v>1837323909.18</v>
+        <v>1847493305.5</v>
       </c>
       <c r="K4" t="n">
-        <v>1926498514.41</v>
+        <v>1908636072.31</v>
       </c>
       <c r="L4" t="n">
-        <v>1837323909.18</v>
+        <v>1847493305.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1837323909.18</v>
+        <v>1847493305.5</v>
       </c>
       <c r="N4" t="n">
-        <v>60537412.94</v>
+        <v>65935375.99</v>
       </c>
       <c r="O4" t="n">
         <v>1007777778</v>
@@ -2034,324 +1996,511 @@
         <v>1007777778</v>
       </c>
       <c r="Q4" t="n">
-        <v>8646604790.549999</v>
+        <v>7465583838.39</v>
       </c>
       <c r="R4" t="n">
-        <v>295172468.58</v>
+        <v>268083184.23</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>22573170.18</v>
+        <v>14064892.26</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>111747920.7</v>
+        <v>84795931.78</v>
       </c>
       <c r="W4" t="n">
-        <v>22573315.47</v>
+        <v>23653164.97</v>
       </c>
       <c r="X4" t="n">
-        <v>89174605.23</v>
+        <v>61142766.81</v>
       </c>
       <c r="Y4" t="n">
-        <v>160851377.7</v>
+        <v>169222360.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>8351432321.97</v>
+        <v>7197500654.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>35197232.68</v>
+        <v>106470092.89</v>
       </c>
       <c r="AB4" t="n">
-        <v>35197232.68</v>
+        <v>106470092.89</v>
       </c>
       <c r="AC4" t="n">
-        <v>2882801.23</v>
+        <v>2303860.56</v>
       </c>
       <c r="AD4" t="n">
-        <v>8226906886.69</v>
+        <v>7026746175.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>8193524967.3</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>30233333.34</v>
-      </c>
+        <v>7024691578.18</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>3148586.05</v>
+        <v>2054597.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>10483928699.73</v>
+        <v>9313077143.889999</v>
       </c>
       <c r="AI4" t="n">
-        <v>441718010.35</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>27308606.63</v>
-      </c>
+        <v>426197673.82</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>16637688.15</v>
+        <v>21001079.72</v>
       </c>
       <c r="AL4" t="n">
-        <v>19223235.33</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1846635</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+        <v>5212428.02</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>1853110</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1853110</v>
+      </c>
       <c r="AP4" t="n">
-        <v>8252386.71</v>
+        <v>8252558.04</v>
       </c>
       <c r="AQ4" t="n">
-        <v>48420728</v>
+        <v>48573122</v>
       </c>
       <c r="AR4" t="n">
-        <v>535962</v>
+        <v>543732</v>
       </c>
       <c r="AS4" t="n">
-        <v>535962</v>
+        <v>543732</v>
       </c>
       <c r="AT4" t="n">
-        <v>346801375.16</v>
+        <v>340761644.04</v>
       </c>
       <c r="AU4" t="n">
-        <v>-107645788.97</v>
+        <v>-138998106.21</v>
       </c>
       <c r="AV4" t="n">
-        <v>454447164.13</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
+        <v>479759750.25</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>49000772.7</v>
+        <v>57280797.38</v>
       </c>
       <c r="AY4" t="n">
-        <v>320162830.99</v>
+        <v>320841455.43</v>
       </c>
       <c r="AZ4" t="n">
-        <v>85283560.44</v>
+        <v>101637497.44</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>10042210689.38</v>
+        <v>8886879470.07</v>
       </c>
       <c r="BC4" t="n">
-        <v>6026696688.51</v>
+        <v>4426745702.71</v>
       </c>
       <c r="BD4" t="n">
-        <v>27542988.95</v>
+        <v>50945132.39</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>64018473.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>64018473.68</v>
       </c>
       <c r="BG4" t="n">
-        <v>3128111550.07</v>
+        <v>3507044966.09</v>
       </c>
       <c r="BH4" t="n">
-        <v>10186154.63</v>
+        <v>12463648.38</v>
       </c>
       <c r="BI4" t="n">
-        <v>849673307.22</v>
+        <v>825661546.8200001</v>
       </c>
       <c r="BJ4" t="n">
-        <v>558851538.15</v>
+        <v>436635183.99</v>
       </c>
       <c r="BK4" t="n">
-        <v>290821769.07</v>
+        <v>389026362.83</v>
       </c>
       <c r="BL4" t="n">
-        <v>290821769.07</v>
-      </c>
+        <v>389026362.83</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>907000000</v>
+        <v>1007777778</v>
       </c>
       <c r="C5" t="n">
-        <v>907000000</v>
+        <v>1007777778</v>
       </c>
       <c r="D5" t="n">
-        <v>174654909.84</v>
+        <v>286946002.54</v>
       </c>
       <c r="E5" t="n">
-        <v>1681141802.05</v>
+        <v>1875707709.59</v>
       </c>
       <c r="F5" t="n">
-        <v>1831990812.72</v>
+        <v>2148050245.07</v>
       </c>
       <c r="G5" t="n">
-        <v>1918024203.02</v>
+        <v>1225538006.53</v>
       </c>
       <c r="H5" t="n">
-        <v>1681141802.05</v>
+        <v>1875707709.59</v>
       </c>
       <c r="I5" t="n">
-        <v>24831103.8</v>
+        <v>15674410.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1682167006.68</v>
+        <v>1876778653.33</v>
       </c>
       <c r="K5" t="n">
-        <v>1799364974.61</v>
+        <v>1876778653.33</v>
       </c>
       <c r="L5" t="n">
-        <v>1682167006.68</v>
+        <v>1876778653.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1682167006.68</v>
+        <v>1876778653.33</v>
       </c>
       <c r="N5" t="n">
-        <v>85633789</v>
+        <v>86784552.34</v>
       </c>
       <c r="O5" t="n">
-        <v>907000000</v>
+        <v>1007777778</v>
       </c>
       <c r="P5" t="n">
-        <v>907000000</v>
+        <v>1007777778</v>
       </c>
       <c r="Q5" t="n">
-        <v>6400934068.24</v>
+        <v>9822590967.549999</v>
       </c>
       <c r="R5" t="n">
-        <v>296728458.21</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1969920.97</v>
-      </c>
+        <v>205673263.81</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1514054.34</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>9859658.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3392469.65</v>
+      </c>
       <c r="V5" t="n">
-        <v>142029071.73</v>
+        <v>15674410.8</v>
       </c>
       <c r="W5" t="n">
-        <v>24831103.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>117197967.93</v>
-      </c>
+        <v>15674410.8</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>151215411.17</v>
+        <v>176746725.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>6104205610.03</v>
+        <v>9616917703.74</v>
       </c>
       <c r="AA5" t="n">
-        <v>32625838.11</v>
+        <v>271271591.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>32625838.11</v>
+        <v>271271591.74</v>
       </c>
       <c r="AC5" t="n">
-        <v>20659015.94</v>
+        <v>6830112.98</v>
       </c>
       <c r="AD5" t="n">
-        <v>5963449501.82</v>
+        <v>9330903236.93</v>
       </c>
       <c r="AE5" t="n">
-        <v>5957433622.58</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
+        <v>9328989181.360001</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>6015879.24</v>
+        <v>1914055.57</v>
       </c>
       <c r="AH5" t="n">
-        <v>8083101074.92</v>
+        <v>11699369620.88</v>
       </c>
       <c r="AI5" t="n">
-        <v>60871261.87</v>
+        <v>856913910.61</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3585849.06</v>
+        <v>409626350.92</v>
       </c>
       <c r="AK5" t="n">
-        <v>7394041.07</v>
+        <v>18349584.85</v>
       </c>
       <c r="AL5" t="n">
-        <v>465835.77</v>
+        <v>11556875.02</v>
       </c>
       <c r="AM5" t="n">
-        <v>1808800</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+        <v>8824536.85</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29736228.88</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>29736228.88</v>
+      </c>
       <c r="AP5" t="n">
-        <v>7036127.76</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>8709774.279999999</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>48467078</v>
+      </c>
       <c r="AR5" t="n">
-        <v>1025204.63</v>
+        <v>1070943.74</v>
       </c>
       <c r="AS5" t="n">
-        <v>1025204.63</v>
+        <v>1070943.74</v>
       </c>
       <c r="AT5" t="n">
-        <v>39555403.58</v>
+        <v>320572538.07</v>
       </c>
       <c r="AU5" t="n">
-        <v>-90825750.59</v>
+        <v>-159468366.64</v>
       </c>
       <c r="AV5" t="n">
-        <v>130381154.17</v>
+        <v>480040904.71</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>50321958.08</v>
+        <v>56359246.37</v>
       </c>
       <c r="AY5" t="n">
-        <v>5177488.74</v>
+        <v>326706062.94</v>
       </c>
       <c r="AZ5" t="n">
-        <v>74881707.34999999</v>
+        <v>96975595.40000001</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>8022229813.05</v>
+        <v>10842455710.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>3959706206.55</v>
+        <v>6778156567.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>294274221.8</v>
+        <v>26869214.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>9531.74</v>
+        <v>409626350.92</v>
       </c>
       <c r="BF5" t="n">
-        <v>9531.74</v>
+        <v>409626350.92</v>
       </c>
       <c r="BG5" t="n">
-        <v>2767589131.41</v>
+        <v>3187993253.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>1960559.2</v>
+        <v>63966816.41</v>
       </c>
       <c r="BI5" t="n">
-        <v>998690162.35</v>
+        <v>785469858.17</v>
       </c>
       <c r="BJ5" t="n">
-        <v>847138634.46</v>
+        <v>376949131.71</v>
       </c>
       <c r="BK5" t="n">
-        <v>151551527.89</v>
+        <v>408520726.46</v>
       </c>
       <c r="BL5" t="n">
-        <v>151551527.89</v>
+        <v>408520726.46</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1007777778</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1007777778</v>
+      </c>
+      <c r="D6" t="n">
+        <v>554780040.89</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1864000347.31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2408469676.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1247171431.05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1864000347.31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11196190.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1864885825.77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1864885825.77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1864885825.77</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1864885825.77</v>
+      </c>
+      <c r="N6" t="n">
+        <v>75766293.29000001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1007777778</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1007777778</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10797408381.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>209133541.19</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1329969.03</v>
+      </c>
+      <c r="T6" t="n">
+        <v>9999149.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2449248.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11196190.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>11196190.5</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>184158983.39</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10588274840.61</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>543583850.39</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>543583850.39</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3361824.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10024067650.73</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>10022002669.85</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>2064980.88</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>12662294207.57</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>826755935.91</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>415831150.44</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>17393665.78</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>9154289.529999999</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>27809985.27</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>27809985.27</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8766789.609999999</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>48068400</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>885478.46</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>885478.46</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>298846176.82</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-158326114.76</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>457172291.58</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>39700857.23</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>325429183.87</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>92042250.48</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11835446271.66</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7480683642.32</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>90525490.31999999</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
+        <v>3327287941.62</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>31158347.54</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>905790849.86</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>425563311.37</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>480227538.49</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>480227538.49</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>63356311.9</v>
       </c>
     </row>
   </sheetData>
@@ -2365,7 +2514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB5"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2634,643 +2783,731 @@
           <t>Receiptsfrom Customers</t>
         </is>
       </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Net Other Investing Changes</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Purchase Of Business</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2331715117.73</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-147779250</v>
-      </c>
-      <c r="D2" t="n">
-        <v>66060000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-16366051.86</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7036460835.63</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4812444833.69</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-4708313.08</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2228724315.02</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-157142182.53</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-52924924.38</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-6454212.08</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-6454212.08</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-81719250</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-81719250</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-147779250</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>66060000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>37785327.96</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>54097175.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>18538411325.09</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-18484314150.08</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>-16311847.05</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>54204.81</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-16366051.86</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>2560.77</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2560.77</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>2348081169.59</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>1235606986</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>679184.29</v>
+      </c>
       <c r="AD2" t="n">
-        <v>2291291865.13</v>
+        <v>1152017940.51</v>
       </c>
       <c r="AE2" t="n">
-        <v>6043964.52</v>
+        <v>834679.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2468016157.41</v>
+        <v>1607227484.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>-356984826.79</v>
+        <v>48667182.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>174216569.99</v>
+        <v>-504711405.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>-16878566.11</v>
+        <v>24931167.08</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7524365.16</v>
+        <v>10993812.94</v>
       </c>
       <c r="AK2" t="n">
-        <v>34280158.06</v>
+        <v>20814612.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>171773.27</v>
+        <v>706482.9</v>
       </c>
       <c r="AM2" t="n">
-        <v>34108384.79</v>
+        <v>20108129.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-9195889.01</v>
+        <v>-55248950.22</v>
       </c>
       <c r="AO2" t="n">
-        <v>308589.19</v>
+        <v>1458080.09</v>
       </c>
       <c r="AP2" t="n">
-        <v>40341.09</v>
+        <v>163754.65</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29826197.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2348081169.59</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-35367637.43</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>327190966.61</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-3332805.9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-3657348325.16</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-486426254.54</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-184529238.44</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-2986392832.18</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5716938971.47</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2939576599.83</v>
-      </c>
+        <v>80211471.47</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>2777362371.64</v>
-      </c>
+        <v>1420813014.24</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1645643325.86</v>
+        <v>1855713204.68</v>
       </c>
       <c r="C3" t="n">
-        <v>-57745054.82</v>
+        <v>-77970968</v>
       </c>
       <c r="D3" t="n">
-        <v>79509286.81999999</v>
+        <v>50000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-28492454.11</v>
+        <v>-69373731.92</v>
       </c>
       <c r="F3" t="n">
-        <v>4812444833.69</v>
+        <v>6316445892.54</v>
       </c>
       <c r="G3" t="n">
-        <v>6316445892.54</v>
+        <v>4106185249.67</v>
       </c>
       <c r="H3" t="n">
-        <v>1035545.34</v>
+        <v>16422634.98</v>
       </c>
       <c r="I3" t="n">
-        <v>-1505036604.19</v>
+        <v>2193838007.89</v>
       </c>
       <c r="J3" t="n">
-        <v>-9788714.960000001</v>
+        <v>119817041.2</v>
       </c>
       <c r="K3" t="n">
-        <v>18346111.74</v>
+        <v>167178705.91</v>
       </c>
       <c r="L3" t="n">
-        <v>-33832459.85</v>
+        <v>-5984768.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-33832459.85</v>
+        <v>-5984768.2</v>
       </c>
       <c r="N3" t="n">
-        <v>21764232</v>
+        <v>-27970968</v>
       </c>
       <c r="O3" t="n">
-        <v>21764232</v>
+        <v>-27970968</v>
       </c>
       <c r="P3" t="n">
-        <v>-57745054.82</v>
+        <v>-77970968</v>
       </c>
       <c r="Q3" t="n">
-        <v>79509286.81999999</v>
+        <v>50000000</v>
       </c>
       <c r="R3" t="n">
-        <v>121902982.52</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>148934030.09</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
       <c r="T3" t="n">
-        <v>150265942.17</v>
+        <v>218301846.08</v>
       </c>
       <c r="U3" t="n">
-        <v>15769443926.97</v>
+        <v>6051742471.45</v>
       </c>
       <c r="V3" t="n">
-        <v>-15619177984.8</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+        <v>-5833440625.37</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" t="n">
-        <v>-28362959.65</v>
+        <v>-69367815.98999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>129494.46</v>
+        <v>5915.93</v>
       </c>
       <c r="AA3" t="n">
-        <v>-28492454.11</v>
+        <v>-69373731.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1617150871.75</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>1925086936.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>304746.41</v>
+      </c>
       <c r="AD3" t="n">
-        <v>-1657388464.18</v>
+        <v>1835358383.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>-4287183.59</v>
+        <v>-9058711.99</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1174562071.76</v>
+        <v>2252962241.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>-64018473.68</v>
+        <v>9531.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>-414520735.15</v>
+        <v>-408554678.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>-14875839.93</v>
+        <v>19258831.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8370982.49</v>
+        <v>9635966.529999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>33758765.43</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>18978611.53</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>534644.63</v>
+      </c>
       <c r="AM3" t="n">
-        <v>33758765.43</v>
+        <v>18443966.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>4821007.84</v>
+        <v>37207961.37</v>
       </c>
       <c r="AO3" t="n">
-        <v>-302679.87</v>
+        <v>-4822830.11</v>
       </c>
       <c r="AP3" t="n">
-        <v>118519.94</v>
+        <v>102386.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7791496.31</v>
+        <v>12381909.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1617150871.75</v>
+        <v>1925086936.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>-34886587.93</v>
+        <v>-62816527.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>337506752.98</v>
+        <v>396594953.36</v>
       </c>
       <c r="AU3" t="n">
-        <v>-525926.05</v>
+        <v>-406322.56</v>
       </c>
       <c r="AV3" t="n">
-        <v>-3941481372.5787</v>
+        <v>-2175124623.05</v>
       </c>
       <c r="AW3" t="n">
-        <v>-1856079065.5287</v>
+        <v>-583262691.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>-182103435.43</v>
+        <v>-178094228.49</v>
       </c>
       <c r="AY3" t="n">
-        <v>-1903298871.62</v>
+        <v>-1413767703.26</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2022236261.82</v>
+        <v>3766839456.21</v>
       </c>
       <c r="BA3" t="n">
-        <v>184840047.44</v>
+        <v>2365459307.25</v>
       </c>
       <c r="BB3" t="n">
-        <v>1837396214.38</v>
-      </c>
+        <v>1401380148.96</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1855713204.68</v>
+        <v>-1645643325.86</v>
       </c>
       <c r="C4" t="n">
-        <v>-77970968</v>
+        <v>-57745054.82</v>
       </c>
       <c r="D4" t="n">
-        <v>50000000</v>
+        <v>79509286.81999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-69373731.92</v>
+        <v>-28492454.11</v>
       </c>
       <c r="F4" t="n">
+        <v>4812444833.69</v>
+      </c>
+      <c r="G4" t="n">
         <v>6316445892.54</v>
       </c>
-      <c r="G4" t="n">
-        <v>4106185249.67</v>
-      </c>
       <c r="H4" t="n">
-        <v>16422634.98</v>
+        <v>1035545.34</v>
       </c>
       <c r="I4" t="n">
-        <v>2193838007.89</v>
+        <v>-1505036604.19</v>
       </c>
       <c r="J4" t="n">
-        <v>119817041.2</v>
+        <v>-9788714.960000001</v>
       </c>
       <c r="K4" t="n">
-        <v>167178705.91</v>
+        <v>18346111.74</v>
       </c>
       <c r="L4" t="n">
-        <v>-5984768.2</v>
+        <v>-33832459.85</v>
       </c>
       <c r="M4" t="n">
-        <v>-5984768.2</v>
+        <v>-33832459.85</v>
       </c>
       <c r="N4" t="n">
-        <v>-27970968</v>
+        <v>21764232</v>
       </c>
       <c r="O4" t="n">
-        <v>-27970968</v>
+        <v>21764232</v>
       </c>
       <c r="P4" t="n">
-        <v>-77970968</v>
+        <v>-57745054.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>50000000</v>
+        <v>79509286.81999999</v>
       </c>
       <c r="R4" t="n">
-        <v>148934030.09</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
+        <v>121902982.52</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>218301846.08</v>
+        <v>150265942.17</v>
       </c>
       <c r="U4" t="n">
-        <v>6051742471.45</v>
+        <v>15769443926.97</v>
       </c>
       <c r="V4" t="n">
-        <v>-5833440625.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
+        <v>-15619177984.8</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-69367815.98999999</v>
+        <v>-28362959.65</v>
       </c>
       <c r="Z4" t="n">
-        <v>5915.93</v>
+        <v>129494.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>-69373731.92</v>
+        <v>-28492454.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>1925086936.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>304746.41</v>
-      </c>
+        <v>-1617150871.75</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>1835358383.13</v>
+        <v>-1657388464.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>-9058711.99</v>
+        <v>-4287183.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>2252962241.53</v>
+        <v>-1174562071.76</v>
       </c>
       <c r="AG4" t="n">
-        <v>9531.74</v>
+        <v>-64018473.68</v>
       </c>
       <c r="AH4" t="n">
-        <v>-408554678.15</v>
+        <v>-414520735.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>19258831.6</v>
+        <v>-14875839.93</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9635966.529999999</v>
+        <v>8370982.49</v>
       </c>
       <c r="AK4" t="n">
-        <v>18978611.53</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>534644.63</v>
-      </c>
+        <v>33758765.43</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>18443966.9</v>
+        <v>33758765.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>37207961.37</v>
+        <v>4821007.84</v>
       </c>
       <c r="AO4" t="n">
-        <v>-4822830.11</v>
+        <v>-302679.87</v>
       </c>
       <c r="AP4" t="n">
-        <v>102386.33</v>
+        <v>118519.94</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12381909.1</v>
+        <v>7791496.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>1925086936.6</v>
+        <v>-1617150871.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>-62816527.36</v>
+        <v>-34886587.93</v>
       </c>
       <c r="AT4" t="n">
-        <v>396594953.36</v>
+        <v>337506752.98</v>
       </c>
       <c r="AU4" t="n">
-        <v>-406322.56</v>
+        <v>-525926.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2175124623.05</v>
+        <v>-3941481372.5787</v>
       </c>
       <c r="AW4" t="n">
-        <v>-583262691.3</v>
+        <v>-1856079065.5287</v>
       </c>
       <c r="AX4" t="n">
-        <v>-178094228.49</v>
+        <v>-182103435.43</v>
       </c>
       <c r="AY4" t="n">
-        <v>-1413767703.26</v>
+        <v>-1903298871.62</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3766839456.21</v>
+        <v>2022236261.82</v>
       </c>
       <c r="BA4" t="n">
-        <v>2365459307.25</v>
+        <v>184840047.44</v>
       </c>
       <c r="BB4" t="n">
-        <v>1401380148.96</v>
-      </c>
+        <v>1837396214.38</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>992265682.35</v>
+        <v>2331715117.73</v>
       </c>
       <c r="C5" t="n">
-        <v>-124980914</v>
+        <v>-147779250</v>
       </c>
       <c r="D5" t="n">
-        <v>239854840</v>
+        <v>66060000</v>
       </c>
       <c r="E5" t="n">
-        <v>-243341303.65</v>
+        <v>-16366051.86</v>
       </c>
       <c r="F5" t="n">
-        <v>4106185249.67</v>
+        <v>7036460835.63</v>
       </c>
       <c r="G5" t="n">
-        <v>2854855864.32</v>
+        <v>4812444833.69</v>
       </c>
       <c r="H5" t="n">
-        <v>-4376690.34</v>
+        <v>-4708313.08</v>
       </c>
       <c r="I5" t="n">
-        <v>1255706075.69</v>
+        <v>2228724315.02</v>
       </c>
       <c r="J5" t="n">
-        <v>44823765.25</v>
+        <v>-157142182.53</v>
       </c>
       <c r="K5" t="n">
-        <v>-2892253.19</v>
+        <v>-52924924.38</v>
       </c>
       <c r="L5" t="n">
-        <v>-51845151.76</v>
+        <v>-6454212.08</v>
       </c>
       <c r="M5" t="n">
-        <v>-51845151.76</v>
+        <v>-6454212.08</v>
       </c>
       <c r="N5" t="n">
-        <v>114873926</v>
+        <v>-81719250</v>
       </c>
       <c r="O5" t="n">
-        <v>114873926</v>
+        <v>-81719250</v>
       </c>
       <c r="P5" t="n">
-        <v>-124980914</v>
+        <v>-147779250</v>
       </c>
       <c r="Q5" t="n">
-        <v>239854840</v>
+        <v>66060000</v>
       </c>
       <c r="R5" t="n">
-        <v>-24724675.56</v>
-      </c>
-      <c r="S5" t="n">
+        <v>37785327.96</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>54097175.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>18538411325.09</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-18484314150.08</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>-16311847.05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>54204.81</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-16366051.86</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2348081169.59</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>2291291865.13</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>6043964.52</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2468016157.41</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-356984826.79</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>174216569.99</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-16878566.11</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>7524365.16</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>34280158.06</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>171773.27</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>34108384.79</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-9195889.01</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>308589.19</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>40341.09</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>29826197.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2348081169.59</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-35367637.43</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>327190966.61</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-3332805.9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-807352064.0700001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-622822825.63</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-184529238.44</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-2986392832.18</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2866942710.38</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2866942710.38</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2777362371.64</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>764377422.45</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-262151821</v>
+      </c>
+      <c r="D6" t="n">
+        <v>234151821</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-7933137.15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3412479712.74</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7036460835.63</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4049787.58</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-3628030910.47</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-54044847.51</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-4312212.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-10077777.78</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-10077777.78</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-28000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-28000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-262151821</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>234151821</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-4346296622.56</v>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>218488350.61</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3336547841.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-3118059490.75</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2560.77</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2560.77</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-243215586.94</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>125716.71</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-243341303.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1235606986</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>679184.29</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1152017940.51</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>834679.11</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1607227484.8</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>48667182.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-504711405.7</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>24931167.08</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>10993812.94</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>20814612.1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>706482.9</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>20108129.2</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-55248950.22</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1458080.09</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>163754.65</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>80211471.47</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1235606986</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-66241905</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>364515103.25</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-538731.14</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-2250613282.05</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-721254995.61</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-173504332.86</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-1355853953.58</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3188485800.94</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1767672786.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1420813014.24</v>
+      <c r="T6" t="n">
+        <v>-19198807.73</v>
+      </c>
+      <c r="U6" t="n">
+        <v>21989885060.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-22009083868.17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-6965792.46</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>967344.6899999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-7933137.15</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>772310559.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-17553808.63</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>252426522.84</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-7278516.93</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1400166669.46</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-1230479723.22</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-169686946.24</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1944883031.78</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1944883031.78</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>-4320132022.37</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3284,7 +3521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ2"/>
+  <dimension ref="A1:EE2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3420,570 +3657,545 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>shortName</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>messageBoardId</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
       <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4005,10 +4217,8 @@
           <t>Nanjing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>210019</t>
-        </is>
+      <c r="D2" t="n">
+        <v>210019</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4075,417 +4285,400 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>8.289999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="T2" t="n">
-        <v>9.17</v>
+        <v>7.35</v>
       </c>
       <c r="U2" t="n">
-        <v>8.25</v>
+        <v>7.36</v>
       </c>
       <c r="V2" t="n">
-        <v>8.58</v>
+        <v>7.64</v>
       </c>
       <c r="W2" t="n">
-        <v>8.289999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="X2" t="n">
-        <v>9.17</v>
+        <v>7.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.25</v>
+        <v>7.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.58</v>
+        <v>7.64</v>
       </c>
       <c r="AA2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>740</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>11473000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11473000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>12279070</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11931445</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11931445</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>7457555968</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6122310892</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>24.598589</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.838200000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.0924</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.0005242464</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>170974816</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>527551511</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>758077778</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.65539</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.00416</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1007777778</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3.980635</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>9.397</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>15298597</v>
+      </c>
+      <c r="BK2" t="n">
         <v>0.01</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1754611200</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.3008</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>837</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12531973</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>12531973</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>14580779</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>10579382</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>10579382</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>8435100160</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>6861529401</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>22.96</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>27.822996</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.4066</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.00048250906</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="AZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>664785920</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0.05046</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>541267367</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>758077778</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.65539</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.00416</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1007777778</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1.859</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4.502421</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1798675200</v>
-      </c>
       <c r="BL2" t="n">
-        <v>1774915200</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.397</v>
+        <v>-0.22513092</v>
       </c>
       <c r="BN2" t="n">
-        <v>15298597</v>
+        <v>0.2568333</v>
       </c>
       <c r="BO2" t="n">
         <v>0.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.193</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-0.12993765</v>
+        <v>1754611200</v>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
       </c>
       <c r="BR2" t="n">
-        <v>0.27697718</v>
-      </c>
-      <c r="BS2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>7791889408</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>7.732</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>21575370</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>303170080</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.008149999999999999</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>299742208</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>3396138496</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.98869</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.22332</v>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>001236.SZ</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>SOHO HOLLY FUTURES CO LTD</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>1781766270</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>finmb_41667528</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-3.014417</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1659663000000</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.23000002</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>7.36 - 7.64</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>12279070</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.1800003</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.02493079</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>7.22 - 16.78</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-9.380001</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.5589988</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-22.513092</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1755179664</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1755525264</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT2" t="n">
         <v>0.01</v>
       </c>
-      <c r="BT2" t="n">
-        <v>1754611200</v>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BV2" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="BX2" t="n">
-        <v>7791889408</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>7.732</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>21575370</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.136</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1.145</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>303170080</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1.152</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>0.00139</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0.008149999999999999</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>299742208</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>3396138496</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0.98869</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>0.22332</v>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>001236.SZ</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="CU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.9650172</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>SOHO HOLLY FUTURES CO LTD</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DU2" t="n">
+        <v>-1.4381995</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.16272539</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-2.6923995</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.26677495</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>Holly Futures Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Soho Holly Futures Co., Ltd.</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>0.07999992</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>8.25 - 8.58</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
-        <v>14580779</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.22000027</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.026993899</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>8.15 - 16.78</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>-8.410000999999999</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.5011919</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-12.993765</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1755179664</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1755525264</v>
-      </c>
-      <c r="DM2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.9630003</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.103182286</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-2.0366</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.19570273</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>Holly Futures Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1659663000000</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>1780038246</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>finmb_41667528</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EG2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
